--- a/visa_appendices/docx/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/docx/DEQUAD_Financial_Model.xlsx
@@ -1525,16 +1525,16 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>320000</v>
+        <v>280000</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>416000</v>
+        <v>370000</v>
       </c>
     </row>
     <row r="7">
@@ -1582,16 +1582,16 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>11988</v>
+        <v>15988</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>185808</v>
+        <v>175808</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>699280</v>
+        <v>659280</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>897076</v>
+        <v>851076</v>
       </c>
     </row>
     <row r="11">
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>10548</v>
+        <v>14548</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>170208</v>
+        <v>160208</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>645280</v>
+        <v>605280</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>826036</v>
+        <v>780036</v>
       </c>
     </row>
     <row r="20">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr"/>
@@ -1988,16 +1988,16 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>-18072</v>
+        <v>-14072</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>-61272</v>
+        <v>-71272</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>66020</v>
+        <v>26020</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>-13324</v>
+        <v>-59324</v>
       </c>
     </row>
     <row r="36">
@@ -2008,17 +2008,17 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>-150.8%</t>
+          <t>-88.0%</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr"/>
@@ -2049,16 +2049,16 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>-18372</v>
+        <v>-14372</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>-62772</v>
+        <v>-72772</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>61520</v>
+        <v>21520</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>-19624</v>
+        <v>-65624</v>
       </c>
     </row>
     <row r="39">
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>-18372</v>
+        <v>-14372</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>-62772</v>
+        <v>-72772</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>61520</v>
+        <v>21520</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-19624</v>
+        <v>-65624</v>
       </c>
     </row>
   </sheetData>
@@ -2163,10 +2163,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>827256</v>
+        <v>821256</v>
       </c>
     </row>
     <row r="7">
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>11988</v>
+        <v>15988</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>185808</v>
+        <v>175808</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>699280</v>
+        <v>659280</v>
       </c>
     </row>
     <row r="13">
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>167988</v>
+        <v>171988</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>940308</v>
+        <v>930308</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>708780</v>
+        <v>668780</v>
       </c>
     </row>
     <row r="15">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>690228</v>
+        <v>680228</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>66520</v>
+        <v>26520</v>
       </c>
     </row>
     <row r="28">
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>827256</v>
+        <v>821256</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>893776</v>
+        <v>847776</v>
       </c>
     </row>
   </sheetData>
@@ -3428,7 +3428,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Cash is positive every month: the £3,000 founder equity covers operating costs until the pre-seed bridge lands in M7 (September). Q1 marketing spend is intentionally £0 — early traction is from founder-led university outreach and the existing beta cohort.</t>
+          <t>Cash is positive every month: the £3,000 founder equity covers operating costs until the pre-seed bridge lands in M7 (December). Q1 marketing spend is intentionally £0 — early traction is from founder-led university outreach and the existing beta cohort.</t>
         </is>
       </c>
     </row>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>827256</v>
+        <v>821256</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>893776</v>
+        <v>847776</v>
       </c>
     </row>
     <row r="11">
@@ -3594,13 +3594,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>137828</v>
+        <v>141828</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>833456</v>
+        <v>827456</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>915776</v>
+        <v>869776</v>
       </c>
     </row>
     <row r="15">
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>138428</v>
+        <v>142428</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>835556</v>
+        <v>829556</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>922376</v>
+        <v>876376</v>
       </c>
     </row>
     <row r="17">
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>831356</v>
+        <v>825356</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>912576</v>
+        <v>866576</v>
       </c>
     </row>
     <row r="24">
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>-18372</v>
+        <v>-14372</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>-81144</v>
+        <v>-87144</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>-19624</v>
+        <v>-65624</v>
       </c>
     </row>
     <row r="28">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>134628</v>
+        <v>138628</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>821856</v>
+        <v>815856</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>883376</v>
+        <v>837376</v>
       </c>
     </row>
     <row r="30">
@@ -3797,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3850,16 +3850,16 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>11988</v>
+        <v>15988</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>185808</v>
+        <v>175808</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>699280</v>
+        <v>659280</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>897076</v>
+        <v>851076</v>
       </c>
     </row>
     <row r="7">
@@ -3914,174 +3914,212 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
+          <t>Price per enrolled student (£/yr)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Average enrolled students per institution</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
           <t>Average contract value (£/yr)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>14000</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Subtotal revenue</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B13" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>280000</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Service 2 — DEQUAD Premium (B2C)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Paying student subs (avg, year)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>6000</v>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>90000</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>320000</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>416000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Service 2 — DEQUAD Premium (B2C)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Paying student subs (avg, year)</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E14" s="10" t="n">
+      <c r="E16" s="10" t="n">
         <v>7700</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Price per student (£/month)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B17" s="10" t="n">
         <v>4.99</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C17" s="10" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D17" s="10" t="n">
         <v>4.99</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E17" s="10" t="n">
         <v>14.97</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Subtotal revenue</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B18" s="12" t="n">
         <v>5988</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C18" s="12" t="n">
         <v>95808</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D18" s="12" t="n">
         <v>359280</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>461076</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Service 3 — NHS ICB pilot</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Number of contracts</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="10" t="n">
+      <c r="B21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E21" s="10" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Average contract value (£/yr)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="10" t="n">
+      <c r="B22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>20000</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E22" s="10" t="n">
         <v>20000</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Subtotal revenue</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12" t="n">
+      <c r="B23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>20000</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>20000</v>
       </c>
     </row>
